--- a/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.01_b0.01_x0.30_Q20_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.01_b0.01_x0.30_Q20_LO.xlsx
@@ -455,10 +455,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02917118302687119</v>
+        <v>0.01558831725939542</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02917118302687119</v>
+        <v>0.01558831725939542</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -469,10 +469,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.02734955911727498</v>
+        <v>0.01445548328594806</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02734955911727498</v>
+        <v>0.01445548328594806</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -483,10 +483,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.025714316985524</v>
+        <v>0.01347004914381907</v>
       </c>
       <c r="C4" t="n">
-        <v>0.025714316985524</v>
+        <v>0.01347004914381907</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -497,10 +497,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.02524661452054687</v>
+        <v>0.01320741525200657</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02524661452054687</v>
+        <v>0.01320741525200657</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -511,10 +511,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.02683382343747448</v>
+        <v>0.01403266190501256</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02683382343747448</v>
+        <v>0.01403266190501256</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -525,10 +525,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.03102341691604336</v>
+        <v>0.01649039356675895</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03102341691604336</v>
+        <v>0.01649039356675895</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -539,10 +539,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.03866777397775619</v>
+        <v>0.02073890919792749</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03866777397775619</v>
+        <v>0.02073890919792749</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -553,10 +553,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.04920023140767596</v>
+        <v>0.02653522342432437</v>
       </c>
       <c r="C9" t="n">
-        <v>0.04920023140767596</v>
+        <v>0.02653522342432437</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -567,10 +567,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.06161454130578815</v>
+        <v>0.03328663654918568</v>
       </c>
       <c r="C10" t="n">
-        <v>0.06161454130578815</v>
+        <v>0.03328663654918568</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -581,10 +581,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.07502704038896167</v>
+        <v>0.04047491336561201</v>
       </c>
       <c r="C11" t="n">
-        <v>0.07502704038896167</v>
+        <v>0.04047491336561201</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -595,10 +595,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.08795011454622181</v>
+        <v>0.04730695552320064</v>
       </c>
       <c r="C12" t="n">
-        <v>0.08795011454622181</v>
+        <v>0.04730695552320064</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -609,10 +609,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.1020689012975569</v>
+        <v>0.05477231129503392</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1020689012975569</v>
+        <v>0.05477231129503392</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -623,10 +623,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.1193402822809615</v>
+        <v>0.06401585579056167</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1193402822809615</v>
+        <v>0.06401585579056167</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -637,10 +637,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.1388723932933775</v>
+        <v>0.07457885141304675</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1388723932933775</v>
+        <v>0.07457885141304675</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -651,10 +651,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.1579869405668937</v>
+        <v>0.0849696834264124</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1579869405668937</v>
+        <v>0.0849696834264124</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -665,10 +665,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.1735776288289157</v>
+        <v>0.09347100842397052</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1735776288289157</v>
+        <v>0.09347100842397052</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -679,10 +679,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.1874723247740308</v>
+        <v>0.1010212535756018</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1874723247740308</v>
+        <v>0.1010212535756018</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -693,10 +693,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.197245391245521</v>
+        <v>0.106309378660632</v>
       </c>
       <c r="C19" t="n">
-        <v>0.197245391245521</v>
+        <v>0.106309378660632</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -707,10 +707,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.2040569776613631</v>
+        <v>0.1099409745760938</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2040569776613631</v>
+        <v>0.1099409745760938</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -721,10 +721,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.2069527517835623</v>
+        <v>0.1114207261964405</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2069527517835623</v>
+        <v>0.1114207261964405</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -735,10 +735,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.208753475714313</v>
+        <v>0.1122902779742959</v>
       </c>
       <c r="C22" t="n">
-        <v>0.208753475714313</v>
+        <v>0.1122902779742959</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -749,10 +749,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.2060551648788544</v>
+        <v>0.110755160426999</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2060551648788544</v>
+        <v>0.110755160426999</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -763,10 +763,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.2028314671733538</v>
+        <v>0.1089652374041156</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2028314671733538</v>
+        <v>0.1089652374041156</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -777,10 +777,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0.1983621840406604</v>
+        <v>0.1065582357129872</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1983621840406604</v>
+        <v>0.1065582357129872</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -791,10 +791,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.1930916871883857</v>
+        <v>0.1037505503501048</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1930916871883857</v>
+        <v>0.1037505503501048</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -805,10 +805,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0.1892736493831922</v>
+        <v>0.1017039175365297</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1892736493831922</v>
+        <v>0.1017039175365297</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -819,10 +819,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0.1803505769680568</v>
+        <v>0.09696317650826576</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1803505769680568</v>
+        <v>0.09696317650826576</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -833,10 +833,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.1757826454913728</v>
+        <v>0.09452804374916833</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1757826454913728</v>
+        <v>0.09452804374916833</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -847,10 +847,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.1743781967048962</v>
+        <v>0.0938241710963682</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1743781967048962</v>
+        <v>0.0938241710963682</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -861,10 +861,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.1717245008218142</v>
+        <v>0.09241765334070226</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1717245008218142</v>
+        <v>0.09241765334070226</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
